--- a/artfynd/A 1364-2026 artfynd.xlsx
+++ b/artfynd/A 1364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133311991</v>
+        <v>133311391</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,24 +946,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Digertäktsgruvan, Digertäktsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536313</v>
+        <v>536259</v>
       </c>
       <c r="R4" t="n">
-        <v>6722593</v>
+        <v>6722536</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -995,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,16 +1023,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133311991</t>
+          <t>https://artportalen.se/Sighting/133311391</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133881073</v>
+        <v>133311418</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,27 +1058,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnets naturreservat, Dlr</t>
+          <t>Digertäktsgruvan, Digertäktsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536544</v>
+        <v>536260</v>
       </c>
       <c r="R5" t="n">
-        <v>6722592</v>
+        <v>6722539</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1094,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,33 +1135,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133881073</t>
+          <t>https://artportalen.se/Sighting/133311418</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133826672</v>
+        <v>133311469</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1186,24 +1170,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
+          <t>Digertäktsgruvan, Digertäktsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536451</v>
+        <v>536262</v>
       </c>
       <c r="R6" t="n">
-        <v>6722592</v>
+        <v>6722542</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,27 +1206,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack gamla,ej färsk kåda</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,44 +1236,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133826672</t>
+          <t>https://artportalen.se/Sighting/133311469</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133881143</v>
+        <v>133311991</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1318,17 +1292,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnets Naturreservat , Dlr</t>
+          <t>Digertäktsgruvan, Digertäktsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536456</v>
+        <v>536313</v>
       </c>
       <c r="R7" t="n">
-        <v>6722594</v>
+        <v>6722593</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1352,27 +1326,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Det är inte mitt fynd men jag vill rapportera att jag sett det. Lugnets naturreservat är styvmoderligt behandlat med sin hänvisning till att bara skogsvårdslagen gäller.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,16 +1367,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133881143</t>
+          <t>https://artportalen.se/Sighting/133311991</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132184715</v>
+        <v>133881073</v>
       </c>
       <c r="B8" t="n">
-        <v>58658</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,16 +1384,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1433,16 +1402,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
+          <t>Lugnets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536526</v>
+        <v>536544</v>
       </c>
       <c r="R8" t="n">
-        <v>6722578</v>
+        <v>6722592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,33 +1487,33 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132184715</t>
+          <t>https://artportalen.se/Sighting/133881073</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133312602</v>
+        <v>133826672</v>
       </c>
       <c r="B9" t="n">
-        <v>58658</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1545,27 +1522,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536396</v>
+        <v>536451</v>
       </c>
       <c r="R9" t="n">
-        <v>6722683</v>
+        <v>6722592</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,22 +1563,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack gamla,ej färsk kåda</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,62 +1598,70 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133312602</t>
+          <t>https://artportalen.se/Sighting/133826672</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133827580</v>
+        <v>133881143</v>
       </c>
       <c r="B10" t="n">
-        <v>111153</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220240</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jungfruberget, Jungfruberget, Dlr</t>
+          <t>Lugnets Naturreservat , Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536576</v>
+        <v>536456</v>
       </c>
       <c r="R10" t="n">
-        <v>6722543</v>
+        <v>6722594</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1703,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Det är inte mitt fynd men jag vill rapportera att jag sett det. Lugnets naturreservat är styvmoderligt behandlat med sin hänvisning till att bara skogsvårdslagen gäller.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,16 +1734,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133827580</t>
+          <t>https://artportalen.se/Sighting/133881143</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133880911</v>
+        <v>132184715</v>
       </c>
       <c r="B11" t="n">
-        <v>111153</v>
+        <v>58658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,38 +1751,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220240</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnets naturreeservat, Dlr</t>
+          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536589</v>
+        <v>536526</v>
       </c>
       <c r="R11" t="n">
-        <v>6722580</v>
+        <v>6722578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,12 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Område med äldre granar och vackra slingrande linneor (som såklart inte blommar än.</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,7 +1829,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1863,6 +1845,360 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132184715</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133312602</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536396</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6722683</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133312602</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133827580</v>
+      </c>
+      <c r="B13" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>536576</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6722543</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133827580</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133880911</v>
+      </c>
+      <c r="B14" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lugnets naturreeservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>536589</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6722580</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Område med äldre granar och vackra slingrande linneor (som såklart inte blommar än.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133880911</t>
         </is>
@@ -1880,6 +2216,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
